--- a/Emerson.xlsx
+++ b/Emerson.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E1547548\Desktop\New folder\pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0D3740-2273-4314-9BAD-B3E3999EF69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C58367-9667-4EEC-98A5-1A5DCB5BE0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -960,11 +960,11 @@
     <col min="2" max="2" width="12.6640625" style="11" customWidth="1"/>
     <col min="3" max="3" width="51.88671875" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" customWidth="1"/>
     <col min="6" max="6" width="27.77734375" customWidth="1"/>
-    <col min="7" max="7" width="13.77734375" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="9" max="9" width="17.77734375" customWidth="1"/>
     <col min="10" max="10" width="21.21875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Emerson.xlsx
+++ b/Emerson.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E1547548\Desktop\New folder\pages\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\E1478337\Desktop\Inspectron1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02C58367-9667-4EEC-98A5-1A5DCB5BE0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DC7671-82CD-440E-9CDF-ECE62933958E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Punch Sheet" sheetId="1" r:id="rId1"/>
@@ -575,38 +575,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="180" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -615,6 +602,19 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -954,21 +954,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J161"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="11" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="11" customWidth="1"/>
-    <col min="3" max="3" width="51.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" customWidth="1"/>
-    <col min="6" max="6" width="27.77734375" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="8.90625" style="11" customWidth="1"/>
+    <col min="2" max="2" width="12.6328125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="51.90625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6328125" customWidth="1"/>
+    <col min="6" max="6" width="27.81640625" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="17.77734375" customWidth="1"/>
-    <col min="10" max="10" width="21.21875" customWidth="1"/>
+    <col min="9" max="9" width="17.81640625" customWidth="1"/>
+    <col min="10" max="10" width="21.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="43.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="3"/>
@@ -976,91 +976,91 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="33"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+    <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="31"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="32"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="33"/>
+    </row>
+    <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="32"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
-    </row>
-    <row r="7" spans="1:10" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="31"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="32"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="33"/>
+    </row>
+    <row r="7" spans="1:10" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="27"/>
-      <c r="G7" s="28" t="s">
+      <c r="F7" s="41"/>
+      <c r="G7" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="27"/>
-      <c r="I7" s="26" t="s">
+      <c r="H7" s="41"/>
+      <c r="I7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="27"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="29"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
+      <c r="J7" s="41"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="28"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
       <c r="E8" s="6" t="s">
         <v>12</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="8"/>
@@ -1092,7 +1092,7 @@
       <c r="I9" s="7"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="8"/>
@@ -1104,7 +1104,7 @@
       <c r="I10" s="7"/>
       <c r="J10" s="9"/>
     </row>
-    <row r="11" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="8"/>
@@ -1116,7 +1116,7 @@
       <c r="I11" s="7"/>
       <c r="J11" s="9"/>
     </row>
-    <row r="12" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="31.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="8"/>
@@ -1128,7 +1128,7 @@
       <c r="I12" s="7"/>
       <c r="J12" s="9"/>
     </row>
-    <row r="13" spans="1:10" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="37.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="8"/>
@@ -1140,7 +1140,7 @@
       <c r="I13" s="7"/>
       <c r="J13" s="9"/>
     </row>
-    <row r="14" spans="1:10" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="25.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="8"/>
@@ -1152,7 +1152,7 @@
       <c r="I14" s="7"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="8"/>
@@ -1164,7 +1164,7 @@
       <c r="I15" s="7"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="8"/>
@@ -1176,7 +1176,7 @@
       <c r="I16" s="7"/>
       <c r="J16" s="9"/>
     </row>
-    <row r="17" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="8"/>
@@ -1188,7 +1188,7 @@
       <c r="I17" s="7"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="30.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="8"/>
@@ -1200,7 +1200,7 @@
       <c r="I18" s="7"/>
       <c r="J18" s="9"/>
     </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="8"/>
@@ -1212,7 +1212,7 @@
       <c r="I19" s="7"/>
       <c r="J19" s="9"/>
     </row>
-    <row r="20" spans="1:10" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="33.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="8"/>
@@ -1224,639 +1224,639 @@
       <c r="I20" s="7"/>
       <c r="J20" s="9"/>
     </row>
-    <row r="21" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F21" s="4"/>
       <c r="H21" s="5"/>
       <c r="J21" s="4"/>
     </row>
-    <row r="22" spans="1:10" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="28.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="F22" s="4"/>
       <c r="H22" s="5"/>
       <c r="J22" s="4"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F23" s="4"/>
       <c r="H23" s="5"/>
       <c r="J23" s="4"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F24" s="4"/>
       <c r="H24" s="5"/>
       <c r="J24" s="4"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F25" s="4"/>
       <c r="H25" s="5"/>
       <c r="J25" s="4"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F26" s="4"/>
       <c r="H26" s="5"/>
       <c r="J26" s="4"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F27" s="4"/>
       <c r="H27" s="5"/>
       <c r="J27" s="4"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F28" s="4"/>
       <c r="H28" s="5"/>
       <c r="J28" s="4"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F29" s="4"/>
       <c r="H29" s="5"/>
       <c r="J29" s="4"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F30" s="4"/>
       <c r="H30" s="5"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F31" s="4"/>
       <c r="H31" s="5"/>
       <c r="J31" s="4"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="F32" s="4"/>
       <c r="H32" s="5"/>
       <c r="J32" s="4"/>
     </row>
-    <row r="33" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F33" s="4"/>
       <c r="H33" s="5"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F34" s="4"/>
       <c r="H34" s="5"/>
       <c r="J34" s="4"/>
     </row>
-    <row r="35" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F35" s="4"/>
       <c r="H35" s="5"/>
       <c r="J35" s="4"/>
     </row>
-    <row r="36" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F36" s="4"/>
       <c r="H36" s="5"/>
       <c r="J36" s="4"/>
     </row>
-    <row r="37" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F37" s="4"/>
       <c r="H37" s="5"/>
       <c r="J37" s="4"/>
     </row>
-    <row r="38" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F38" s="4"/>
       <c r="H38" s="5"/>
       <c r="J38" s="4"/>
     </row>
-    <row r="39" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F39" s="4"/>
       <c r="H39" s="5"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F40" s="4"/>
       <c r="H40" s="5"/>
       <c r="J40" s="4"/>
     </row>
-    <row r="41" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F41" s="4"/>
       <c r="H41" s="5"/>
       <c r="J41" s="4"/>
     </row>
-    <row r="42" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F42" s="4"/>
       <c r="H42" s="5"/>
       <c r="J42" s="4"/>
     </row>
-    <row r="43" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F43" s="4"/>
       <c r="H43" s="5"/>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F44" s="4"/>
       <c r="H44" s="5"/>
       <c r="J44" s="4"/>
     </row>
-    <row r="45" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F45" s="4"/>
       <c r="H45" s="5"/>
       <c r="J45" s="4"/>
     </row>
-    <row r="46" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F46" s="4"/>
       <c r="H46" s="5"/>
       <c r="J46" s="4"/>
     </row>
-    <row r="47" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F47" s="4"/>
       <c r="H47" s="5"/>
       <c r="J47" s="4"/>
     </row>
-    <row r="48" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F48" s="4"/>
       <c r="H48" s="5"/>
       <c r="J48" s="4"/>
     </row>
-    <row r="49" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F49" s="4"/>
       <c r="H49" s="5"/>
       <c r="J49" s="4"/>
     </row>
-    <row r="50" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F50" s="4"/>
       <c r="H50" s="5"/>
       <c r="J50" s="4"/>
     </row>
-    <row r="51" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F51" s="4"/>
       <c r="H51" s="5"/>
       <c r="J51" s="4"/>
     </row>
-    <row r="52" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F52" s="4"/>
       <c r="H52" s="5"/>
       <c r="J52" s="4"/>
     </row>
-    <row r="53" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F53" s="4"/>
       <c r="H53" s="5"/>
       <c r="J53" s="4"/>
     </row>
-    <row r="54" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F54" s="4"/>
       <c r="H54" s="5"/>
       <c r="J54" s="4"/>
     </row>
-    <row r="55" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F55" s="4"/>
       <c r="H55" s="5"/>
       <c r="J55" s="4"/>
     </row>
-    <row r="56" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F56" s="4"/>
       <c r="H56" s="5"/>
       <c r="J56" s="4"/>
     </row>
-    <row r="57" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F57" s="4"/>
       <c r="H57" s="5"/>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F58" s="4"/>
       <c r="H58" s="5"/>
       <c r="J58" s="4"/>
     </row>
-    <row r="59" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F59" s="4"/>
       <c r="H59" s="5"/>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F60" s="4"/>
       <c r="H60" s="5"/>
       <c r="J60" s="4"/>
     </row>
-    <row r="61" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F61" s="4"/>
       <c r="H61" s="5"/>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F62" s="4"/>
       <c r="H62" s="5"/>
       <c r="J62" s="4"/>
     </row>
-    <row r="63" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F63" s="4"/>
       <c r="H63" s="5"/>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F64" s="4"/>
       <c r="H64" s="5"/>
       <c r="J64" s="4"/>
     </row>
-    <row r="65" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F65" s="4"/>
       <c r="H65" s="5"/>
       <c r="J65" s="4"/>
     </row>
-    <row r="66" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F66" s="4"/>
       <c r="H66" s="5"/>
       <c r="J66" s="4"/>
     </row>
-    <row r="67" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F67" s="4"/>
       <c r="H67" s="5"/>
       <c r="J67" s="4"/>
     </row>
-    <row r="68" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F68" s="4"/>
       <c r="H68" s="5"/>
       <c r="J68" s="4"/>
     </row>
-    <row r="69" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F69" s="4"/>
       <c r="H69" s="5"/>
       <c r="J69" s="4"/>
     </row>
-    <row r="70" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F70" s="4"/>
       <c r="H70" s="5"/>
       <c r="J70" s="4"/>
     </row>
-    <row r="71" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F71" s="4"/>
       <c r="H71" s="5"/>
       <c r="J71" s="4"/>
     </row>
-    <row r="72" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F72" s="4"/>
       <c r="H72" s="5"/>
       <c r="J72" s="4"/>
     </row>
-    <row r="73" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F73" s="4"/>
       <c r="H73" s="5"/>
       <c r="J73" s="4"/>
     </row>
-    <row r="74" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F74" s="4"/>
       <c r="H74" s="5"/>
       <c r="J74" s="4"/>
     </row>
-    <row r="75" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F75" s="4"/>
       <c r="H75" s="5"/>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F76" s="4"/>
       <c r="H76" s="5"/>
       <c r="J76" s="4"/>
     </row>
-    <row r="77" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F77" s="4"/>
       <c r="H77" s="5"/>
       <c r="J77" s="4"/>
     </row>
-    <row r="78" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F78" s="4"/>
       <c r="H78" s="5"/>
       <c r="J78" s="4"/>
     </row>
-    <row r="79" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F79" s="4"/>
       <c r="H79" s="5"/>
       <c r="J79" s="4"/>
     </row>
-    <row r="80" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F80" s="4"/>
       <c r="H80" s="5"/>
       <c r="J80" s="4"/>
     </row>
-    <row r="81" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F81" s="4"/>
       <c r="H81" s="5"/>
       <c r="J81" s="4"/>
     </row>
-    <row r="82" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F82" s="4"/>
       <c r="H82" s="5"/>
       <c r="J82" s="4"/>
     </row>
-    <row r="83" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F83" s="4"/>
       <c r="H83" s="5"/>
       <c r="J83" s="4"/>
     </row>
-    <row r="84" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F84" s="4"/>
       <c r="H84" s="5"/>
       <c r="J84" s="4"/>
     </row>
-    <row r="85" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F85" s="4"/>
       <c r="H85" s="5"/>
       <c r="J85" s="4"/>
     </row>
-    <row r="86" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F86" s="4"/>
       <c r="H86" s="5"/>
       <c r="J86" s="4"/>
     </row>
-    <row r="87" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F87" s="4"/>
       <c r="H87" s="5"/>
       <c r="J87" s="4"/>
     </row>
-    <row r="88" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F88" s="4"/>
       <c r="H88" s="5"/>
       <c r="J88" s="4"/>
     </row>
-    <row r="89" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F89" s="4"/>
       <c r="H89" s="5"/>
       <c r="J89" s="4"/>
     </row>
-    <row r="90" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F90" s="4"/>
       <c r="H90" s="5"/>
       <c r="J90" s="4"/>
     </row>
-    <row r="91" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F91" s="4"/>
       <c r="H91" s="5"/>
       <c r="J91" s="4"/>
     </row>
-    <row r="92" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F92" s="4"/>
       <c r="H92" s="5"/>
       <c r="J92" s="4"/>
     </row>
-    <row r="93" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F93" s="4"/>
       <c r="H93" s="5"/>
       <c r="J93" s="4"/>
     </row>
-    <row r="94" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F94" s="4"/>
       <c r="H94" s="5"/>
       <c r="J94" s="4"/>
     </row>
-    <row r="95" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F95" s="4"/>
       <c r="H95" s="5"/>
       <c r="J95" s="4"/>
     </row>
-    <row r="96" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F96" s="4"/>
       <c r="H96" s="5"/>
       <c r="J96" s="4"/>
     </row>
-    <row r="97" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F97" s="4"/>
       <c r="H97" s="5"/>
       <c r="J97" s="4"/>
     </row>
-    <row r="98" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F98" s="4"/>
       <c r="H98" s="5"/>
       <c r="J98" s="4"/>
     </row>
-    <row r="99" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F99" s="4"/>
       <c r="H99" s="5"/>
       <c r="J99" s="4"/>
     </row>
-    <row r="100" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F100" s="4"/>
       <c r="H100" s="5"/>
       <c r="J100" s="4"/>
     </row>
-    <row r="101" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F101" s="4"/>
       <c r="H101" s="5"/>
       <c r="J101" s="4"/>
     </row>
-    <row r="102" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F102" s="4"/>
       <c r="H102" s="5"/>
       <c r="J102" s="4"/>
     </row>
-    <row r="103" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F103" s="4"/>
       <c r="H103" s="5"/>
       <c r="J103" s="4"/>
     </row>
-    <row r="104" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F104" s="4"/>
       <c r="H104" s="5"/>
       <c r="J104" s="4"/>
     </row>
-    <row r="105" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F105" s="4"/>
       <c r="H105" s="5"/>
       <c r="J105" s="4"/>
     </row>
-    <row r="106" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="6:10" x14ac:dyDescent="0.35">
       <c r="F106" s="4"/>
       <c r="H106" s="5"/>
       <c r="J106" s="4"/>
     </row>
-    <row r="107" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="6:10" x14ac:dyDescent="0.35">
       <c r="H107" s="5"/>
       <c r="J107" s="4"/>
     </row>
-    <row r="108" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="6:10" x14ac:dyDescent="0.35">
       <c r="H108" s="5"/>
       <c r="J108" s="4"/>
     </row>
-    <row r="109" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="6:10" x14ac:dyDescent="0.35">
       <c r="H109" s="5"/>
       <c r="J109" s="4"/>
     </row>
-    <row r="110" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="6:10" x14ac:dyDescent="0.35">
       <c r="H110" s="5"/>
       <c r="J110" s="4"/>
     </row>
-    <row r="111" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="6:10" x14ac:dyDescent="0.35">
       <c r="H111" s="5"/>
       <c r="J111" s="4"/>
     </row>
-    <row r="112" spans="6:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="6:10" x14ac:dyDescent="0.35">
       <c r="H112" s="5"/>
       <c r="J112" s="4"/>
     </row>
-    <row r="113" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H113" s="5"/>
       <c r="J113" s="4"/>
     </row>
-    <row r="114" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H114" s="5"/>
       <c r="J114" s="4"/>
     </row>
-    <row r="115" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H115" s="5"/>
       <c r="J115" s="4"/>
     </row>
-    <row r="116" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H116" s="5"/>
       <c r="J116" s="4"/>
     </row>
-    <row r="117" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H117" s="5"/>
       <c r="J117" s="4"/>
     </row>
-    <row r="118" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H118" s="5"/>
       <c r="J118" s="4"/>
     </row>
-    <row r="119" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H119" s="5"/>
       <c r="J119" s="4"/>
     </row>
-    <row r="120" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H120" s="5"/>
       <c r="J120" s="4"/>
     </row>
-    <row r="121" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H121" s="5"/>
       <c r="J121" s="4"/>
     </row>
-    <row r="122" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H122" s="5"/>
       <c r="J122" s="4"/>
     </row>
-    <row r="123" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H123" s="5"/>
       <c r="J123" s="4"/>
     </row>
-    <row r="124" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H124" s="5"/>
       <c r="J124" s="4"/>
     </row>
-    <row r="125" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H125" s="5"/>
       <c r="J125" s="4"/>
     </row>
-    <row r="126" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H126" s="5"/>
       <c r="J126" s="4"/>
     </row>
-    <row r="127" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H127" s="5"/>
       <c r="J127" s="4"/>
     </row>
-    <row r="128" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H128" s="5"/>
       <c r="J128" s="4"/>
     </row>
-    <row r="129" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H129" s="5"/>
       <c r="J129" s="4"/>
     </row>
-    <row r="130" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H130" s="5"/>
       <c r="J130" s="4"/>
     </row>
-    <row r="131" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H131" s="5"/>
       <c r="J131" s="4"/>
     </row>
-    <row r="132" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H132" s="5"/>
       <c r="J132" s="4"/>
     </row>
-    <row r="133" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H133" s="5"/>
       <c r="J133" s="4"/>
     </row>
-    <row r="134" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H134" s="5"/>
       <c r="J134" s="4"/>
     </row>
-    <row r="135" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H135" s="5"/>
       <c r="J135" s="4"/>
     </row>
-    <row r="136" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H136" s="5"/>
       <c r="J136" s="4"/>
     </row>
-    <row r="137" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H137" s="5"/>
       <c r="J137" s="4"/>
     </row>
-    <row r="138" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H138" s="5"/>
       <c r="J138" s="4"/>
     </row>
-    <row r="139" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H139" s="5"/>
       <c r="J139" s="4"/>
     </row>
-    <row r="140" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H140" s="5"/>
       <c r="J140" s="4"/>
     </row>
-    <row r="141" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H141" s="5"/>
       <c r="J141" s="4"/>
     </row>
-    <row r="142" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H142" s="5"/>
       <c r="J142" s="4"/>
     </row>
-    <row r="143" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H143" s="5"/>
       <c r="J143" s="4"/>
     </row>
-    <row r="144" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H144" s="5"/>
       <c r="J144" s="4"/>
     </row>
-    <row r="145" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H145" s="5"/>
       <c r="J145" s="4"/>
     </row>
-    <row r="146" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H146" s="5"/>
       <c r="J146" s="4"/>
     </row>
-    <row r="147" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H147" s="5"/>
     </row>
-    <row r="148" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H148" s="5"/>
     </row>
-    <row r="149" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H149" s="5"/>
     </row>
-    <row r="150" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H150" s="5"/>
     </row>
-    <row r="151" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H151" s="5"/>
     </row>
-    <row r="152" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H152" s="5"/>
     </row>
-    <row r="153" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H153" s="5"/>
     </row>
-    <row r="154" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H154" s="5"/>
     </row>
-    <row r="155" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H155" s="5"/>
     </row>
-    <row r="156" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H156" s="5"/>
     </row>
-    <row r="157" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H157" s="5"/>
     </row>
-    <row r="158" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H158" s="5"/>
     </row>
-    <row r="159" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H159" s="5"/>
     </row>
-    <row r="160" spans="8:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="8:10" x14ac:dyDescent="0.35">
       <c r="H160" s="5"/>
     </row>
-    <row r="161" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="8:8" x14ac:dyDescent="0.35">
       <c r="H161" s="5"/>
     </row>
   </sheetData>
@@ -1875,10 +1875,7 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="E7:F7"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9:D408" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Wrong Wiring , Incomplete Asembly, Material Shortfall , Incomplete wiring , Design Error , Faulty Equipment , Workmanship error, Wrong Assembly"</formula1>
-    </dataValidation>
+  <dataValidations count="4">
     <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F9:F663" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>46026</formula1>
     </dataValidation>
@@ -1916,23 +1913,24 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:K162"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="48.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="48.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>15</v>
       </c>
@@ -1967,13 +1965,13 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="K2" t="e">
         <f>UPPER(TRIM(#REF!))</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1985,13 +1983,13 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="K4" t="e">
         <f>UPPER(TRIM(#REF!))</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -2009,19 +2007,19 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="K6" t="e">
         <f>UPPER(TRIM(#REF!))</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="K7" t="e">
         <f>UPPER(TRIM(#REF!))</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2048,7 +2046,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="E9" t="s">
         <v>12</v>
       </c>
@@ -2072,7 +2070,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1</v>
       </c>
@@ -2097,7 +2095,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2122,7 +2120,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>3</v>
       </c>
@@ -2147,7 +2145,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>4</v>
       </c>
@@ -2172,7 +2170,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>5</v>
       </c>
@@ -2197,7 +2195,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>6</v>
       </c>
@@ -2222,7 +2220,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>7</v>
       </c>
@@ -2247,7 +2245,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>8</v>
       </c>
@@ -2272,7 +2270,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>9</v>
       </c>
@@ -2297,7 +2295,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>10</v>
       </c>
@@ -2322,7 +2320,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>11</v>
       </c>
@@ -2335,7 +2333,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>12</v>
       </c>
@@ -2348,7 +2346,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B22">
         <f>'Punch Sheet'!B21</f>
         <v>0</v>
@@ -2358,7 +2356,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B23">
         <f>'Punch Sheet'!B22</f>
         <v>0</v>
@@ -2368,7 +2366,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B24">
         <f>'Punch Sheet'!B23</f>
         <v>0</v>
@@ -2378,7 +2376,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B25">
         <f>'Punch Sheet'!B24</f>
         <v>0</v>
@@ -2388,7 +2386,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B26">
         <f>'Punch Sheet'!B25</f>
         <v>0</v>
@@ -2398,7 +2396,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B27">
         <f>'Punch Sheet'!B26</f>
         <v>0</v>
@@ -2408,7 +2406,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B28">
         <f>'Punch Sheet'!B27</f>
         <v>0</v>
@@ -2418,7 +2416,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B29">
         <f>'Punch Sheet'!B28</f>
         <v>0</v>
@@ -2428,7 +2426,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B30">
         <f>'Punch Sheet'!B29</f>
         <v>0</v>
@@ -2438,7 +2436,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B31">
         <f>'Punch Sheet'!B30</f>
         <v>0</v>
@@ -2448,7 +2446,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B32">
         <f>'Punch Sheet'!B31</f>
         <v>0</v>
@@ -2458,7 +2456,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B33">
         <f>'Punch Sheet'!B32</f>
         <v>0</v>
@@ -2468,7 +2466,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B34">
         <f>'Punch Sheet'!B33</f>
         <v>0</v>
@@ -2478,7 +2476,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B35">
         <f>'Punch Sheet'!B34</f>
         <v>0</v>
@@ -2488,7 +2486,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B36">
         <f>'Punch Sheet'!B35</f>
         <v>0</v>
@@ -2498,7 +2496,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B37">
         <f>'Punch Sheet'!B36</f>
         <v>0</v>
@@ -2508,7 +2506,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B38">
         <f>'Punch Sheet'!B37</f>
         <v>0</v>
@@ -2518,7 +2516,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B39">
         <f>'Punch Sheet'!B38</f>
         <v>0</v>
@@ -2528,7 +2526,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B40">
         <f>'Punch Sheet'!B39</f>
         <v>0</v>
@@ -2538,7 +2536,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B41">
         <f>'Punch Sheet'!B40</f>
         <v>0</v>
@@ -2548,7 +2546,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B42">
         <f>'Punch Sheet'!B41</f>
         <v>0</v>
@@ -2558,7 +2556,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B43">
         <f>'Punch Sheet'!B42</f>
         <v>0</v>
@@ -2568,7 +2566,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B44">
         <f>'Punch Sheet'!B43</f>
         <v>0</v>
@@ -2578,7 +2576,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B45">
         <f>'Punch Sheet'!B44</f>
         <v>0</v>
@@ -2588,7 +2586,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B46">
         <f>'Punch Sheet'!B45</f>
         <v>0</v>
@@ -2598,7 +2596,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B47">
         <f>'Punch Sheet'!B46</f>
         <v>0</v>
@@ -2608,7 +2606,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B48">
         <f>'Punch Sheet'!B47</f>
         <v>0</v>
@@ -2618,7 +2616,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B49">
         <f>'Punch Sheet'!B48</f>
         <v>0</v>
@@ -2628,7 +2626,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B50">
         <f>'Punch Sheet'!B49</f>
         <v>0</v>
@@ -2638,7 +2636,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B51">
         <f>'Punch Sheet'!B50</f>
         <v>0</v>
@@ -2648,7 +2646,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B52">
         <f>'Punch Sheet'!B51</f>
         <v>0</v>
@@ -2658,7 +2656,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B53">
         <f>'Punch Sheet'!B52</f>
         <v>0</v>
@@ -2668,7 +2666,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B54">
         <f>'Punch Sheet'!B53</f>
         <v>0</v>
@@ -2678,7 +2676,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B55">
         <f>'Punch Sheet'!B54</f>
         <v>0</v>
@@ -2688,7 +2686,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B56">
         <f>'Punch Sheet'!B55</f>
         <v>0</v>
@@ -2698,7 +2696,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B57">
         <f>'Punch Sheet'!B56</f>
         <v>0</v>
@@ -2708,7 +2706,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B58">
         <f>'Punch Sheet'!B57</f>
         <v>0</v>
@@ -2718,7 +2716,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B59">
         <f>'Punch Sheet'!B58</f>
         <v>0</v>
@@ -2728,7 +2726,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B60">
         <f>'Punch Sheet'!B59</f>
         <v>0</v>
@@ -2738,7 +2736,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B61">
         <f>'Punch Sheet'!B60</f>
         <v>0</v>
@@ -2748,7 +2746,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B62">
         <f>'Punch Sheet'!B61</f>
         <v>0</v>
@@ -2758,7 +2756,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B63">
         <f>'Punch Sheet'!B62</f>
         <v>0</v>
@@ -2768,7 +2766,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B64">
         <f>'Punch Sheet'!B63</f>
         <v>0</v>
@@ -2778,7 +2776,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B65">
         <f>'Punch Sheet'!B64</f>
         <v>0</v>
@@ -2788,7 +2786,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B66">
         <f>'Punch Sheet'!B65</f>
         <v>0</v>
@@ -2798,7 +2796,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B67">
         <f>'Punch Sheet'!B66</f>
         <v>0</v>
@@ -2808,7 +2806,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B68">
         <f>'Punch Sheet'!B67</f>
         <v>0</v>
@@ -2818,7 +2816,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B69">
         <f>'Punch Sheet'!B68</f>
         <v>0</v>
@@ -2828,7 +2826,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B70">
         <f>'Punch Sheet'!B69</f>
         <v>0</v>
@@ -2838,7 +2836,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B71">
         <f>'Punch Sheet'!B70</f>
         <v>0</v>
@@ -2848,7 +2846,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B72">
         <f>'Punch Sheet'!B71</f>
         <v>0</v>
@@ -2858,7 +2856,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B73">
         <f>'Punch Sheet'!B72</f>
         <v>0</v>
@@ -2868,7 +2866,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B74">
         <f>'Punch Sheet'!B73</f>
         <v>0</v>
@@ -2878,7 +2876,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B75">
         <f>'Punch Sheet'!B74</f>
         <v>0</v>
@@ -2888,7 +2886,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B76">
         <f>'Punch Sheet'!B75</f>
         <v>0</v>
@@ -2898,7 +2896,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B77">
         <f>'Punch Sheet'!B76</f>
         <v>0</v>
@@ -2908,7 +2906,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B78">
         <f>'Punch Sheet'!B77</f>
         <v>0</v>
@@ -2918,7 +2916,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B79">
         <f>'Punch Sheet'!B78</f>
         <v>0</v>
@@ -2928,7 +2926,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B80">
         <f>'Punch Sheet'!B79</f>
         <v>0</v>
@@ -2938,7 +2936,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B81">
         <f>'Punch Sheet'!B80</f>
         <v>0</v>
@@ -2948,7 +2946,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B82">
         <f>'Punch Sheet'!B81</f>
         <v>0</v>
@@ -2958,7 +2956,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B83">
         <f>'Punch Sheet'!B82</f>
         <v>0</v>
@@ -2968,7 +2966,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B84">
         <f>'Punch Sheet'!B83</f>
         <v>0</v>
@@ -2978,7 +2976,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B85">
         <f>'Punch Sheet'!B84</f>
         <v>0</v>
@@ -2988,7 +2986,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B86">
         <f>'Punch Sheet'!B85</f>
         <v>0</v>
@@ -2998,7 +2996,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B87">
         <f>'Punch Sheet'!B86</f>
         <v>0</v>
@@ -3008,7 +3006,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B88">
         <f>'Punch Sheet'!B87</f>
         <v>0</v>
@@ -3018,7 +3016,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B89">
         <f>'Punch Sheet'!B88</f>
         <v>0</v>
@@ -3028,7 +3026,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B90">
         <f>'Punch Sheet'!B89</f>
         <v>0</v>
@@ -3038,7 +3036,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B91">
         <f>'Punch Sheet'!B90</f>
         <v>0</v>
@@ -3048,7 +3046,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B92">
         <f>'Punch Sheet'!B91</f>
         <v>0</v>
@@ -3058,7 +3056,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B93">
         <f>'Punch Sheet'!B92</f>
         <v>0</v>
@@ -3068,7 +3066,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B94">
         <f>'Punch Sheet'!B93</f>
         <v>0</v>
@@ -3078,7 +3076,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B95">
         <f>'Punch Sheet'!B94</f>
         <v>0</v>
@@ -3088,7 +3086,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B96">
         <f>'Punch Sheet'!B95</f>
         <v>0</v>
@@ -3098,7 +3096,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B97">
         <f>'Punch Sheet'!B96</f>
         <v>0</v>
@@ -3108,7 +3106,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B98">
         <f>'Punch Sheet'!B97</f>
         <v>0</v>
@@ -3118,7 +3116,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="99" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B99">
         <f>'Punch Sheet'!B98</f>
         <v>0</v>
@@ -3128,7 +3126,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="100" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B100">
         <f>'Punch Sheet'!B99</f>
         <v>0</v>
@@ -3138,7 +3136,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="101" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B101">
         <f>'Punch Sheet'!B100</f>
         <v>0</v>
@@ -3148,7 +3146,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="102" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B102">
         <f>'Punch Sheet'!B101</f>
         <v>0</v>
@@ -3158,7 +3156,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="103" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B103">
         <f>'Punch Sheet'!B102</f>
         <v>0</v>
@@ -3168,7 +3166,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="104" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B104">
         <f>'Punch Sheet'!B103</f>
         <v>0</v>
@@ -3178,7 +3176,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="105" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B105">
         <f>'Punch Sheet'!B104</f>
         <v>0</v>
@@ -3188,7 +3186,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="106" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B106">
         <f>'Punch Sheet'!B105</f>
         <v>0</v>
@@ -3198,7 +3196,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="107" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B107">
         <f>'Punch Sheet'!B106</f>
         <v>0</v>
@@ -3208,7 +3206,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="108" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B108">
         <f>'Punch Sheet'!B107</f>
         <v>0</v>
@@ -3218,7 +3216,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="109" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B109">
         <f>'Punch Sheet'!B108</f>
         <v>0</v>
@@ -3228,7 +3226,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="110" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B110">
         <f>'Punch Sheet'!B109</f>
         <v>0</v>
@@ -3238,7 +3236,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="111" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B111">
         <f>'Punch Sheet'!B110</f>
         <v>0</v>
@@ -3248,7 +3246,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B112">
         <f>'Punch Sheet'!B111</f>
         <v>0</v>
@@ -3258,7 +3256,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="113" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B113">
         <f>'Punch Sheet'!B112</f>
         <v>0</v>
@@ -3268,7 +3266,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="114" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B114">
         <f>'Punch Sheet'!B113</f>
         <v>0</v>
@@ -3278,7 +3276,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B115">
         <f>'Punch Sheet'!B114</f>
         <v>0</v>
@@ -3288,7 +3286,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="116" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B116">
         <f>'Punch Sheet'!B115</f>
         <v>0</v>
@@ -3298,7 +3296,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="117" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B117">
         <f>'Punch Sheet'!B116</f>
         <v>0</v>
@@ -3308,7 +3306,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="118" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B118">
         <f>'Punch Sheet'!B117</f>
         <v>0</v>
@@ -3318,7 +3316,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="119" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B119">
         <f>'Punch Sheet'!B118</f>
         <v>0</v>
@@ -3328,7 +3326,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="120" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B120">
         <f>'Punch Sheet'!B119</f>
         <v>0</v>
@@ -3338,7 +3336,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="121" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B121">
         <f>'Punch Sheet'!B120</f>
         <v>0</v>
@@ -3348,7 +3346,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="122" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B122">
         <f>'Punch Sheet'!B121</f>
         <v>0</v>
@@ -3358,7 +3356,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="123" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B123">
         <f>'Punch Sheet'!B122</f>
         <v>0</v>
@@ -3368,7 +3366,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="124" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B124">
         <f>'Punch Sheet'!B123</f>
         <v>0</v>
@@ -3378,7 +3376,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="125" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B125">
         <f>'Punch Sheet'!B124</f>
         <v>0</v>
@@ -3388,7 +3386,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="126" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B126">
         <f>'Punch Sheet'!B125</f>
         <v>0</v>
@@ -3398,7 +3396,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B127">
         <f>'Punch Sheet'!B126</f>
         <v>0</v>
@@ -3408,7 +3406,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="128" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B128">
         <f>'Punch Sheet'!B127</f>
         <v>0</v>
@@ -3418,7 +3416,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="129" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B129">
         <f>'Punch Sheet'!B128</f>
         <v>0</v>
@@ -3428,7 +3426,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="130" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B130">
         <f>'Punch Sheet'!B129</f>
         <v>0</v>
@@ -3438,7 +3436,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="131" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B131">
         <f>'Punch Sheet'!B130</f>
         <v>0</v>
@@ -3448,7 +3446,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="132" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B132">
         <f>'Punch Sheet'!B131</f>
         <v>0</v>
@@ -3458,7 +3456,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="133" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B133">
         <f>'Punch Sheet'!B132</f>
         <v>0</v>
@@ -3468,7 +3466,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="134" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B134">
         <f>'Punch Sheet'!B133</f>
         <v>0</v>
@@ -3478,7 +3476,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="135" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B135">
         <f>'Punch Sheet'!B134</f>
         <v>0</v>
@@ -3488,7 +3486,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="136" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B136">
         <f>'Punch Sheet'!B135</f>
         <v>0</v>
@@ -3498,7 +3496,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="137" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B137">
         <f>'Punch Sheet'!B136</f>
         <v>0</v>
@@ -3508,7 +3506,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="138" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B138">
         <f>'Punch Sheet'!B137</f>
         <v>0</v>
@@ -3518,7 +3516,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="139" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B139">
         <f>'Punch Sheet'!B138</f>
         <v>0</v>
@@ -3528,7 +3526,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="140" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B140">
         <f>'Punch Sheet'!B139</f>
         <v>0</v>
@@ -3538,7 +3536,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="141" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B141">
         <f>'Punch Sheet'!B140</f>
         <v>0</v>
@@ -3548,7 +3546,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="142" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B142">
         <f>'Punch Sheet'!B141</f>
         <v>0</v>
@@ -3558,7 +3556,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="143" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B143">
         <f>'Punch Sheet'!B142</f>
         <v>0</v>
@@ -3568,7 +3566,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="144" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B144">
         <f>'Punch Sheet'!B143</f>
         <v>0</v>
@@ -3578,7 +3576,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="145" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B145">
         <f>'Punch Sheet'!B144</f>
         <v>0</v>
@@ -3588,7 +3586,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="146" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B146">
         <f>'Punch Sheet'!B145</f>
         <v>0</v>
@@ -3598,7 +3596,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="147" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B147">
         <f>'Punch Sheet'!B146</f>
         <v>0</v>
@@ -3608,7 +3606,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="148" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B148">
         <f>'Punch Sheet'!B147</f>
         <v>0</v>
@@ -3618,7 +3616,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="149" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B149">
         <f>'Punch Sheet'!B148</f>
         <v>0</v>
@@ -3628,7 +3626,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="150" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B150">
         <f>'Punch Sheet'!B149</f>
         <v>0</v>
@@ -3638,7 +3636,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="151" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B151">
         <f>'Punch Sheet'!B150</f>
         <v>0</v>
@@ -3648,7 +3646,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="152" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B152">
         <f>'Punch Sheet'!B151</f>
         <v>0</v>
@@ -3658,7 +3656,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="153" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B153">
         <f>'Punch Sheet'!B152</f>
         <v>0</v>
@@ -3668,7 +3666,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="154" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B154">
         <f>'Punch Sheet'!B153</f>
         <v>0</v>
@@ -3678,7 +3676,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="155" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B155">
         <f>'Punch Sheet'!B154</f>
         <v>0</v>
@@ -3688,7 +3686,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="156" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B156">
         <f>'Punch Sheet'!B155</f>
         <v>0</v>
@@ -3698,7 +3696,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="157" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B157">
         <f>'Punch Sheet'!B156</f>
         <v>0</v>
@@ -3708,7 +3706,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="158" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B158">
         <f>'Punch Sheet'!B157</f>
         <v>0</v>
@@ -3718,7 +3716,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="159" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B159">
         <f>'Punch Sheet'!B158</f>
         <v>0</v>
@@ -3728,7 +3726,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="160" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B160">
         <f>'Punch Sheet'!B159</f>
         <v>0</v>
@@ -3738,7 +3736,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="161" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B161">
         <f>'Punch Sheet'!B160</f>
         <v>0</v>
@@ -3748,7 +3746,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="162" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B162">
         <f>'Punch Sheet'!B161</f>
         <v>0</v>
@@ -3765,25 +3763,25 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="11" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="11" customWidth="1"/>
+    <col min="1" max="1" width="12.36328125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" style="11" customWidth="1"/>
     <col min="3" max="3" width="32" style="11" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="18.6640625" style="11" customWidth="1"/>
-    <col min="6" max="6" width="33.33203125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" style="11" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" style="11" customWidth="1"/>
-    <col min="10" max="10" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="18.6328125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="33.36328125" style="11" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" style="11" customWidth="1"/>
+    <col min="10" max="10" width="13.453125" customWidth="1"/>
     <col min="12" max="12" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="24"/>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -3794,7 +3792,7 @@
       <c r="H1" s="24"/>
       <c r="I1" s="25"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="24"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
@@ -3805,61 +3803,61 @@
       <c r="H2" s="24"/>
       <c r="I2" s="25"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="40" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
       <c r="I4" s="22"/>
       <c r="J4" s="21"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="33"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="32"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="22"/>
       <c r="J5" s="21"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="40" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="42" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
       <c r="I6" s="22"/>
       <c r="J6" s="21"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="33"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" s="32"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
       <c r="I7" s="22"/>
       <c r="J7" s="21"/>
     </row>
-    <row r="10" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="6"/>
       <c r="B10" s="23" t="s">
         <v>6</v>
@@ -3880,8 +3878,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="39" t="s">
+    <row r="11" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="29" t="s">
         <v>48</v>
       </c>
       <c r="B11" s="13">
@@ -3899,8 +3897,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="29"/>
+    <row r="12" spans="1:12" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="28"/>
       <c r="B12" s="6">
         <v>2</v>
       </c>
@@ -3916,8 +3914,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="37" t="s">
+    <row r="13" spans="1:12" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="26" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="16">
@@ -3935,8 +3933,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="38"/>
+    <row r="14" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="27"/>
       <c r="B14" s="6">
         <v>4</v>
       </c>
@@ -3952,8 +3950,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="38"/>
+    <row r="15" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="27"/>
       <c r="B15" s="6">
         <v>5</v>
       </c>
@@ -3969,8 +3967,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="38"/>
+    <row r="16" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="27"/>
       <c r="B16" s="6">
         <v>6</v>
       </c>
@@ -3986,8 +3984,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="38"/>
+    <row r="17" spans="1:12" ht="96.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="27"/>
       <c r="B17" s="6">
         <v>7</v>
       </c>
@@ -4003,8 +4001,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
+    <row r="18" spans="1:12" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="27"/>
       <c r="B18" s="6">
         <v>8</v>
       </c>
@@ -4020,8 +4018,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="29"/>
+    <row r="19" spans="1:12" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="28"/>
       <c r="B19" s="6">
         <v>9</v>
       </c>
@@ -4037,8 +4035,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37" t="s">
+    <row r="20" spans="1:12" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="26" t="s">
         <v>59</v>
       </c>
       <c r="B20" s="6">
@@ -4056,8 +4054,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="38"/>
+    <row r="21" spans="1:12" ht="82.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="27"/>
       <c r="B21" s="6">
         <v>11</v>
       </c>
@@ -4073,8 +4071,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="38"/>
+    <row r="22" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="27"/>
       <c r="B22" s="6">
         <v>12</v>
       </c>
@@ -4090,8 +4088,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="38"/>
+    <row r="23" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
       <c r="B23" s="6">
         <v>13</v>
       </c>
@@ -4107,8 +4105,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="38"/>
+    <row r="24" spans="1:12" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="27"/>
       <c r="B24" s="6">
         <v>14</v>
       </c>
@@ -4124,8 +4122,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="38"/>
+    <row r="25" spans="1:12" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="27"/>
       <c r="B25" s="6">
         <v>15</v>
       </c>
@@ -4141,8 +4139,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="38"/>
+    <row r="26" spans="1:12" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="27"/>
       <c r="B26" s="6">
         <v>16</v>
       </c>
@@ -4158,8 +4156,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="38"/>
+    <row r="27" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="27"/>
       <c r="B27" s="6">
         <v>17</v>
       </c>
@@ -4175,8 +4173,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="29"/>
+    <row r="28" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="28"/>
       <c r="B28" s="6">
         <v>18</v>
       </c>
@@ -4192,8 +4190,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="37" t="s">
+    <row r="29" spans="1:12" ht="82.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="26" t="s">
         <v>69</v>
       </c>
       <c r="B29" s="6">
@@ -4211,8 +4209,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="38"/>
+    <row r="30" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="27"/>
       <c r="B30" s="6">
         <v>20</v>
       </c>
@@ -4228,8 +4226,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="38"/>
+    <row r="31" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="27"/>
       <c r="B31" s="6">
         <v>21</v>
       </c>
@@ -4245,8 +4243,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="38"/>
+    <row r="32" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="27"/>
       <c r="B32" s="6">
         <v>22</v>
       </c>
@@ -4262,8 +4260,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="38"/>
+    <row r="33" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="27"/>
       <c r="B33" s="6">
         <v>23</v>
       </c>
@@ -4279,8 +4277,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="38"/>
+    <row r="34" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="27"/>
       <c r="B34" s="6">
         <v>24</v>
       </c>
@@ -4296,8 +4294,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="38"/>
+    <row r="35" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="27"/>
       <c r="B35" s="6">
         <v>25</v>
       </c>
@@ -4313,8 +4311,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="29"/>
+    <row r="36" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="28"/>
       <c r="B36" s="6">
         <v>26</v>
       </c>
@@ -4330,8 +4328,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="37" t="s">
+    <row r="37" spans="1:12" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="26" t="s">
         <v>78</v>
       </c>
       <c r="B37" s="6">
@@ -4349,8 +4347,8 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="38"/>
+    <row r="38" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="27"/>
       <c r="B38" s="6">
         <v>28</v>
       </c>
@@ -4366,8 +4364,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="38"/>
+    <row r="39" spans="1:12" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="27"/>
       <c r="B39" s="6">
         <v>29</v>
       </c>
@@ -4383,8 +4381,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="38"/>
+    <row r="40" spans="1:12" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="27"/>
       <c r="B40" s="6">
         <v>30</v>
       </c>
@@ -4400,8 +4398,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="29"/>
+    <row r="41" spans="1:12" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="28"/>
       <c r="B41" s="6">
         <v>31</v>
       </c>
@@ -4417,7 +4415,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D42" s="20"/>
       <c r="E42" s="19"/>
     </row>
